--- a/Result/profitability/3018.xlsx
+++ b/Result/profitability/3018.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3975</v>
+        <v>-0.6</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.595</v>
+        <v>-10.7075</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.41375</v>
+        <v>-0.5437500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.390000000000001</v>
+        <v>-8.775</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.35375</v>
+        <v>-0.525</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.67</v>
+        <v>-8.768750000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3200000000000001</v>
+        <v>-0.42875</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.115</v>
+        <v>-5.674999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2375</v>
+        <v>-0.2275</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1137500000000002</v>
+        <v>-1.105</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.015</v>
+        <v>-0.225</v>
       </c>
       <c r="N7" t="n">
-        <v>6.78125</v>
+        <v>5.155</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03499999999999999</v>
+        <v>-0.13875</v>
       </c>
       <c r="N8" t="n">
-        <v>11.62</v>
+        <v>7.9475</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.28</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08375000000000002</v>
+        <v>0.08375</v>
       </c>
       <c r="N9" t="n">
         <v>15.945</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>75</v>
+      </c>
+      <c r="D75" t="n">
+        <v>99</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-31.96</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-56</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-74.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-57</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-113</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-113</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.58375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-8.51375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.238805970149254</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-29.38</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>11.38759689922481</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-20.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.78397212543554</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
